--- a/public/templates/DentalHandHeld_Test_Data_Template_WithTimer.xlsx
+++ b/public/templates/DentalHandHeld_Test_Data_Template_WithTimer.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <workbookPr codeName="ThisWorkbook"/>
   <sheets>
-    <sheet name="With Timer" sheetId="1" r:id="rId1"/>
+    <sheet name="Dental HandHeld (Timer)" sheetId="1" r:id="rId1"/>
   </sheets>
 </workbook>
 </file>
@@ -397,16 +397,36 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N47"/>
+  <dimension ref="A1:R46"/>
+  <cols>
+    <col min="1" max="1" width="18.83203125" customWidth="1"/>
+    <col min="2" max="2" width="18.83203125" customWidth="1"/>
+    <col min="3" max="3" width="18.83203125" customWidth="1"/>
+    <col min="4" max="4" width="18.83203125" customWidth="1"/>
+    <col min="5" max="5" width="18.83203125" customWidth="1"/>
+    <col min="6" max="6" width="18.83203125" customWidth="1"/>
+    <col min="7" max="7" width="18.83203125" customWidth="1"/>
+    <col min="8" max="8" width="18.83203125" customWidth="1"/>
+    <col min="9" max="9" width="18.83203125" customWidth="1"/>
+    <col min="10" max="10" width="18.83203125" customWidth="1"/>
+    <col min="11" max="11" width="18.83203125" customWidth="1"/>
+    <col min="12" max="12" width="18.83203125" customWidth="1"/>
+    <col min="13" max="13" width="18.83203125" customWidth="1"/>
+    <col min="14" max="14" width="18.83203125" customWidth="1"/>
+    <col min="15" max="15" width="18.83203125" customWidth="1"/>
+    <col min="16" max="16" width="18.83203125" customWidth="1"/>
+    <col min="17" max="17" width="18.83203125" customWidth="1"/>
+    <col min="18" max="18" width="18.83203125" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>TEST: ACCURACY OF OPERATING POTENTIAL</v>
+        <v>TEST: ACCURACY OF OPERATING POTENTIAL &amp; TIME</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Tolerance Sign</v>
+        <v>kVp Tolerance Sign</v>
       </c>
       <c r="B2" t="str">
         <v>±</v>
@@ -414,261 +434,296 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>Tolerance Value (kVp)</v>
+        <v>kVp Tolerance Value</v>
       </c>
       <c r="B3" t="str">
-        <v>5</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>Applied kVp</v>
+        <v>Time Tolerance Sign</v>
       </c>
       <c r="B4" t="str">
-        <v>mA 1</v>
-      </c>
-      <c r="C4" t="str">
-        <v>mA 2</v>
+        <v>±</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>60</v>
+        <v>Time Tolerance Value (%)</v>
       </c>
       <c r="B5" t="str">
-        <v>60.1</v>
-      </c>
-      <c r="C5" t="str">
-        <v>60.2</v>
+        <v>10</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>80</v>
+        <v>Applied kVp</v>
       </c>
       <c r="B6" t="str">
-        <v>80.1</v>
+        <v>Set Time</v>
       </c>
       <c r="C6" t="str">
-        <v>80.2</v>
+        <v>Meas 1 kVp</v>
+      </c>
+      <c r="D6" t="str">
+        <v>Meas 1 Time</v>
+      </c>
+      <c r="E6" t="str">
+        <v>Meas 2 kVp</v>
+      </c>
+      <c r="F6" t="str">
+        <v>Meas 2 Time</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="B7" t="str">
-        <v>100.1</v>
+        <v>0.100</v>
       </c>
       <c r="C7" t="str">
-        <v>100.2</v>
+        <v>60.1</v>
+      </c>
+      <c r="D7" t="str">
+        <v>0.101</v>
+      </c>
+      <c r="E7" t="str">
+        <v>60.2</v>
+      </c>
+      <c r="F7" t="str">
+        <v>0.099</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>120</v>
+        <v>80</v>
       </c>
       <c r="B8" t="str">
-        <v>120.1</v>
+        <v>0.100</v>
       </c>
       <c r="C8" t="str">
-        <v>120.2</v>
+        <v>80.1</v>
+      </c>
+      <c r="D8" t="str">
+        <v>0.101</v>
+      </c>
+      <c r="E8" t="str">
+        <v>80.2</v>
+      </c>
+      <c r="F8" t="str">
+        <v>0.099</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>100</v>
+      </c>
+      <c r="B9" t="str">
+        <v>0.100</v>
+      </c>
+      <c r="C9" t="str">
+        <v>100.1</v>
+      </c>
+      <c r="D9" t="str">
+        <v>0.101</v>
+      </c>
+      <c r="E9" t="str">
+        <v>100.2</v>
+      </c>
+      <c r="F9" t="str">
+        <v>0.099</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>TEST: TOTAL FILTRATION</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>Total Filtration Measured (mm Al)</v>
-      </c>
-      <c r="B11" t="str">
-        <v>2.1</v>
+        <v>120</v>
+      </c>
+      <c r="B10" t="str">
+        <v>0.100</v>
+      </c>
+      <c r="C10" t="str">
+        <v>120.1</v>
+      </c>
+      <c r="D10" t="str">
+        <v>0.101</v>
+      </c>
+      <c r="E10" t="str">
+        <v>120.2</v>
+      </c>
+      <c r="F10" t="str">
+        <v>0.099</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>Total Filtration Required (mm Al)</v>
-      </c>
-      <c r="B12" t="str">
-        <v>2.0</v>
+        <v>TEST: TOTAL FILTRATION</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>Total Filtration At kVp</v>
+        <v>Total Filtration Measured (mm Al)</v>
       </c>
       <c r="B13" t="str">
-        <v>80</v>
+        <v>2.1</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>Total Filtration Required (mm Al)</v>
+      </c>
+      <c r="B14" t="str">
+        <v>2.0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>TEST: ACCURACY OF IRRADIATION TIME</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="str">
-        <v>FDD (cm)</v>
-      </c>
-      <c r="B16" t="str">
-        <v>kV</v>
-      </c>
-      <c r="C16" t="str">
-        <v>mA</v>
-      </c>
-      <c r="D16" t="str">
-        <v>Set Time (mSec)</v>
-      </c>
-      <c r="E16" t="str">
-        <v>mA Station 1 Time</v>
-      </c>
-      <c r="F16" t="str">
-        <v>mA Station 2 Time</v>
+        <v>Total Filtration At kVp</v>
+      </c>
+      <c r="B15" t="str">
+        <v>80</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>100</v>
-      </c>
-      <c r="B17" t="str">
-        <v>80</v>
-      </c>
-      <c r="C17" t="str">
-        <v>100</v>
-      </c>
-      <c r="D17" t="str">
-        <v>100</v>
-      </c>
-      <c r="E17" t="str">
-        <v>101</v>
-      </c>
-      <c r="F17" t="str">
-        <v>99</v>
+        <v>TEST: LINEARITY OF TIME</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>100</v>
+        <v>FDD (cm)</v>
       </c>
       <c r="B18" t="str">
+        <v>kV</v>
+      </c>
+      <c r="C18" t="str">
+        <v>mA</v>
+      </c>
+      <c r="D18" t="str">
+        <v>Time Station (sec)</v>
+      </c>
+      <c r="E18" t="str">
+        <v>Measured mR 1</v>
+      </c>
+      <c r="F18" t="str">
+        <v>Measured mR 2</v>
+      </c>
+      <c r="G18" t="str">
+        <v>Measured mR 3</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>100</v>
+      </c>
+      <c r="B19" t="str">
         <v>80</v>
       </c>
-      <c r="C18" t="str">
-        <v>100</v>
-      </c>
-      <c r="D18" t="str">
-        <v>200</v>
-      </c>
-      <c r="E18" t="str">
-        <v>201</v>
-      </c>
-      <c r="F18" t="str">
-        <v>199</v>
+      <c r="C19" t="str">
+        <v>100</v>
+      </c>
+      <c r="D19" t="str">
+        <v>0.1</v>
+      </c>
+      <c r="E19" t="str">
+        <v>10.1</v>
+      </c>
+      <c r="F19" t="str">
+        <v>10.2</v>
+      </c>
+      <c r="G19" t="str">
+        <v>10.1</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>TEST: LINEARITY OF TIME</v>
+        <v>100</v>
+      </c>
+      <c r="B20" t="str">
+        <v>80</v>
+      </c>
+      <c r="C20" t="str">
+        <v>100</v>
+      </c>
+      <c r="D20" t="str">
+        <v>0.2</v>
+      </c>
+      <c r="E20" t="str">
+        <v>20.1</v>
+      </c>
+      <c r="F20" t="str">
+        <v>20.2</v>
+      </c>
+      <c r="G20" t="str">
+        <v>20.1</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>FDD (cm)</v>
+        <v>Tolerance Operator</v>
       </c>
       <c r="B21" t="str">
-        <v>kV</v>
-      </c>
-      <c r="C21" t="str">
-        <v>mA</v>
-      </c>
-      <c r="D21" t="str">
-        <v>Time Station (sec)</v>
-      </c>
-      <c r="E21" t="str">
-        <v>Measured mR 1</v>
-      </c>
-      <c r="F21" t="str">
-        <v>Measured mR 2</v>
-      </c>
-      <c r="G21" t="str">
-        <v>Measured mR 3</v>
+        <v>&lt;=</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>100</v>
+        <v>Tolerance Value (CoL)</v>
       </c>
       <c r="B22" t="str">
-        <v>80</v>
-      </c>
-      <c r="C22" t="str">
-        <v>100</v>
-      </c>
-      <c r="D22" t="str">
         <v>0.1</v>
       </c>
-      <c r="E22" t="str">
-        <v>10.1</v>
-      </c>
-      <c r="F22" t="str">
-        <v>10.2</v>
-      </c>
-      <c r="G22" t="str">
-        <v>10.1</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="str">
-        <v>100</v>
-      </c>
-      <c r="B23" t="str">
-        <v>80</v>
-      </c>
-      <c r="C23" t="str">
-        <v>100</v>
-      </c>
-      <c r="D23" t="str">
-        <v>0.2</v>
-      </c>
-      <c r="E23" t="str">
-        <v>20.1</v>
-      </c>
-      <c r="F23" t="str">
-        <v>20.2</v>
-      </c>
-      <c r="G23" t="str">
-        <v>20.1</v>
+    </row>
+    <row r="24">
+      <c r="A24" t="str">
+        <v>TEST: LINEARITY OF mA LOADING</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>TEST: LINEARITY OF mA LOADING</v>
+        <v>FDD (cm)</v>
+      </c>
+      <c r="B25" t="str">
+        <v>kV</v>
+      </c>
+      <c r="C25" t="str">
+        <v>Time</v>
+      </c>
+      <c r="D25" t="str">
+        <v>mA Station</v>
+      </c>
+      <c r="E25" t="str">
+        <v>Measured mR 1</v>
+      </c>
+      <c r="F25" t="str">
+        <v>Measured mR 2</v>
+      </c>
+      <c r="G25" t="str">
+        <v>Measured mR 3</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>FDD (cm)</v>
+        <v>100</v>
       </c>
       <c r="B26" t="str">
-        <v>kV</v>
+        <v>80</v>
       </c>
       <c r="C26" t="str">
-        <v>Time</v>
+        <v>0.5</v>
       </c>
       <c r="D26" t="str">
-        <v>mA Station</v>
+        <v>50</v>
       </c>
       <c r="E26" t="str">
-        <v>Measured mR 1</v>
+        <v>5.1</v>
       </c>
       <c r="F26" t="str">
-        <v>Measured mR 2</v>
+        <v>5.2</v>
       </c>
       <c r="G26" t="str">
-        <v>Measured mR 3</v>
+        <v>5.1</v>
       </c>
     </row>
     <row r="27">
@@ -682,16 +737,16 @@
         <v>0.5</v>
       </c>
       <c r="D27" t="str">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="E27" t="str">
-        <v>5.1</v>
+        <v>10.1</v>
       </c>
       <c r="F27" t="str">
-        <v>5.2</v>
+        <v>10.2</v>
       </c>
       <c r="G27" t="str">
-        <v>5.1</v>
+        <v>10.1</v>
       </c>
     </row>
     <row r="28">
@@ -705,16 +760,16 @@
         <v>0.5</v>
       </c>
       <c r="D28" t="str">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="E28" t="str">
-        <v>10.1</v>
+        <v>20.1</v>
       </c>
       <c r="F28" t="str">
-        <v>10.2</v>
+        <v>20.2</v>
       </c>
       <c r="G28" t="str">
-        <v>10.1</v>
+        <v>20.1</v>
       </c>
     </row>
     <row r="29">
@@ -728,234 +783,267 @@
         <v>0.5</v>
       </c>
       <c r="D29" t="str">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="E29" t="str">
-        <v>20.1</v>
+        <v>30.1</v>
       </c>
       <c r="F29" t="str">
-        <v>20.2</v>
+        <v>30.2</v>
       </c>
       <c r="G29" t="str">
-        <v>20.1</v>
+        <v>30.1</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>100</v>
+        <v>Tolerance Operator</v>
       </c>
       <c r="B30" t="str">
-        <v>80</v>
-      </c>
-      <c r="C30" t="str">
-        <v>0.5</v>
-      </c>
-      <c r="D30" t="str">
-        <v>300</v>
-      </c>
-      <c r="E30" t="str">
-        <v>30.1</v>
-      </c>
-      <c r="F30" t="str">
-        <v>30.2</v>
-      </c>
-      <c r="G30" t="str">
-        <v>30.1</v>
+        <v>&lt;=</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>Tolerance Operator</v>
+        <v>Tolerance Value (CoL)</v>
       </c>
       <c r="B31" t="str">
-        <v>&lt;=</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="str">
-        <v>Tolerance Value (CoL)</v>
-      </c>
-      <c r="B32" t="str">
         <v>0.1</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="str">
+        <v>TEST: CONSISTENCY OF RADIATION OUTPUT</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>TEST: CONSISTENCY OF RADIATION OUTPUT</v>
+        <v>Tolerance Operator</v>
+      </c>
+      <c r="B34" t="str">
+        <v>&lt;=</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>Tolerance Operator</v>
+        <v>Tolerance Value (CoV)</v>
       </c>
       <c r="B35" t="str">
-        <v>&lt;=</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>Tolerance Value (CoV)</v>
+        <v>FFD</v>
       </c>
       <c r="B36" t="str">
-        <v>0.05</v>
+        <v>Test kV</v>
+      </c>
+      <c r="C36" t="str">
+        <v>Test mAs</v>
+      </c>
+      <c r="D36" t="str">
+        <v>Meas 1</v>
+      </c>
+      <c r="E36" t="str">
+        <v>Meas 2</v>
+      </c>
+      <c r="F36" t="str">
+        <v>Meas 3</v>
+      </c>
+      <c r="G36" t="str">
+        <v>Mean</v>
+      </c>
+      <c r="H36" t="str">
+        <v>CoV</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>FDD (cm)</v>
+        <v>40</v>
       </c>
       <c r="B37" t="str">
-        <v>Test kV</v>
+        <v>120</v>
       </c>
       <c r="C37" t="str">
-        <v>Test mAs</v>
+        <v>100</v>
       </c>
       <c r="D37" t="str">
-        <v>Meas 1</v>
+        <v>50.1</v>
       </c>
       <c r="E37" t="str">
-        <v>Meas 2</v>
+        <v>50.2</v>
       </c>
       <c r="F37" t="str">
-        <v>Meas 3</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="str">
-        <v>40</v>
-      </c>
-      <c r="B38" t="str">
-        <v>120</v>
-      </c>
-      <c r="C38" t="str">
-        <v>100</v>
-      </c>
-      <c r="D38" t="str">
         <v>50.1</v>
       </c>
-      <c r="E38" t="str">
-        <v>50.2</v>
-      </c>
-      <c r="F38" t="str">
-        <v>50.1</v>
+      <c r="G37" t="str">
+        <v>50.13</v>
+      </c>
+      <c r="H37" t="str">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="str">
+        <v>TEST: RADIATION LEAKAGE LEVEL</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>TEST: TUBE HOUSING LEAKAGE</v>
+        <v>Distance</v>
+      </c>
+      <c r="B40" t="str">
+        <v>kV</v>
+      </c>
+      <c r="C40" t="str">
+        <v>mA</v>
+      </c>
+      <c r="D40" t="str">
+        <v>Time</v>
+      </c>
+      <c r="E40" t="str">
+        <v>Location</v>
+      </c>
+      <c r="F40" t="str">
+        <v>Front</v>
+      </c>
+      <c r="G40" t="str">
+        <v>Back</v>
+      </c>
+      <c r="H40" t="str">
+        <v>Left</v>
+      </c>
+      <c r="I40" t="str">
+        <v>Right</v>
+      </c>
+      <c r="J40" t="str">
+        <v>Top</v>
+      </c>
+      <c r="K40" t="str">
+        <v>Max</v>
+      </c>
+      <c r="L40" t="str">
+        <v>Unit</v>
+      </c>
+      <c r="M40" t="str">
+        <v>Remark</v>
+      </c>
+      <c r="N40" t="str">
+        <v>Workload</v>
+      </c>
+      <c r="O40" t="str">
+        <v>Workload Unit</v>
+      </c>
+      <c r="P40" t="str">
+        <v>Tolerance Value</v>
+      </c>
+      <c r="Q40" t="str">
+        <v>Tolerance Operator</v>
+      </c>
+      <c r="R40" t="str">
+        <v>Tolerance Time</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>Distance</v>
+        <v>100</v>
       </c>
       <c r="B41" t="str">
-        <v>kV</v>
+        <v>120</v>
       </c>
       <c r="C41" t="str">
-        <v>mA</v>
+        <v>100</v>
       </c>
       <c r="D41" t="str">
-        <v>Time</v>
+        <v>1</v>
       </c>
       <c r="E41" t="str">
-        <v>Workload</v>
+        <v>Tube</v>
       </c>
       <c r="F41" t="str">
-        <v>Tolerance Value</v>
+        <v>0.01</v>
       </c>
       <c r="G41" t="str">
-        <v>Tolerance Operator</v>
+        <v>0.02</v>
       </c>
       <c r="H41" t="str">
-        <v>Tolerance Time</v>
+        <v>0.01</v>
       </c>
       <c r="I41" t="str">
-        <v>Location</v>
+        <v>0.01</v>
       </c>
       <c r="J41" t="str">
-        <v>Front</v>
+        <v>0.02</v>
       </c>
       <c r="K41" t="str">
-        <v>Back</v>
+        <v>0.02</v>
       </c>
       <c r="L41" t="str">
-        <v>Left</v>
+        <v>mR/h</v>
       </c>
       <c r="M41" t="str">
-        <v>Right</v>
+        <v/>
       </c>
       <c r="N41" t="str">
-        <v>Top</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="str">
-        <v>100</v>
-      </c>
-      <c r="B42" t="str">
-        <v>120</v>
-      </c>
-      <c r="C42" t="str">
-        <v>100</v>
-      </c>
-      <c r="D42" t="str">
+        <v>500</v>
+      </c>
+      <c r="O41" t="str">
+        <v>mA in one hour</v>
+      </c>
+      <c r="P41" t="str">
         <v>1</v>
       </c>
-      <c r="E42" t="str">
-        <v>500</v>
-      </c>
-      <c r="F42" t="str">
+      <c r="Q41" t="str">
+        <v>&lt;=</v>
+      </c>
+      <c r="R41" t="str">
         <v>1</v>
       </c>
-      <c r="G42" t="str">
-        <v>&lt;=</v>
-      </c>
-      <c r="H42" t="str">
-        <v>1</v>
-      </c>
-      <c r="I42" t="str">
-        <v>Tube</v>
-      </c>
-      <c r="J42" t="str">
-        <v>0.01</v>
-      </c>
-      <c r="K42" t="str">
-        <v>0.02</v>
-      </c>
-      <c r="L42" t="str">
-        <v>0.01</v>
-      </c>
-      <c r="M42" t="str">
-        <v>0.01</v>
-      </c>
-      <c r="N42" t="str">
-        <v>0.02</v>
+    </row>
+    <row r="43">
+      <c r="A43" t="str">
+        <v>TEST: RADIATION PROTECTION SURVEY REPORT</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>TEST: RADIATION PROTECTION SURVEY REPORT</v>
+        <v>kV</v>
+      </c>
+      <c r="B44" t="str">
+        <v>mA</v>
+      </c>
+      <c r="C44" t="str">
+        <v>Time</v>
+      </c>
+      <c r="D44" t="str">
+        <v>Workload</v>
+      </c>
+      <c r="E44" t="str">
+        <v>Location</v>
+      </c>
+      <c r="F44" t="str">
+        <v>mR/hr</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>kV</v>
+        <v>80</v>
       </c>
       <c r="B45" t="str">
-        <v>mA</v>
+        <v>100</v>
       </c>
       <c r="C45" t="str">
-        <v>Time</v>
+        <v>0.5</v>
       </c>
       <c r="D45" t="str">
-        <v>Workload</v>
+        <v>500</v>
       </c>
       <c r="E45" t="str">
-        <v>Location</v>
+        <v>Control Console (Operator Position)</v>
       </c>
       <c r="F45" t="str">
-        <v>mR/hr</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="46">
@@ -969,38 +1057,18 @@
         <v>0.5</v>
       </c>
       <c r="D46" t="str">
-        <v>5000</v>
+        <v>500</v>
       </c>
       <c r="E46" t="str">
-        <v>Control Console (Operator Position)</v>
+        <v>Outside Patient Entrance Door</v>
       </c>
       <c r="F46" t="str">
-        <v>0.02</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="str">
-        <v>80</v>
-      </c>
-      <c r="B47" t="str">
-        <v>100</v>
-      </c>
-      <c r="C47" t="str">
-        <v>0.5</v>
-      </c>
-      <c r="D47" t="str">
-        <v>5000</v>
-      </c>
-      <c r="E47" t="str">
-        <v>Outside Patient Entrance Door</v>
-      </c>
-      <c r="F47" t="str">
         <v>0.01</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:N47"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:R46"/>
   </ignoredErrors>
 </worksheet>
 </file>